--- a/mormugao/test.xlsx
+++ b/mormugao/test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,221 +425,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BERTH</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>VESSEL NAME</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ARR/BER/NO</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CARGO/I/E</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AGENT/SHPR-RECVR/STEVHOOK/</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>QTY I</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ETD</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>REMARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>BERTH-04</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>VISHAL HIRA/92.37
 /    3.500   .  .</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>01.04 00:01
 01.04 00:01</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>/I</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>V.M. S</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Unnamed: 9</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Unnamed: 10</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>30.04</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Unnamed: 14</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>BERTH-05</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>OCEAN
 HELIOS/182.93   .
 .</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>14.04 05:03
 14.04 07:06
 14.04 05:03</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>HR COI/E</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>BENLIN/JSW ST</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>/
-3491</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>/
-406</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>/
-2408</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>/
-8305</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="F3" t="n">
         <v>37934</v>
       </c>
-      <c r="L2" t="n">
-        <v>27056</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10878</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>18.04/
 16:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>BERTH-06</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>LUCKY
 SUNDAY/229.00   .
 .</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>15.04 07:43
 16.04 19:50
 15.04 07:43</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>C.COAL/I</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>HIRALA</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>/
-18700</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>/
-18700</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
+      <c r="F4" t="n">
         <v>72855</v>
       </c>
-      <c r="L3" t="n">
-        <v>18700</v>
-      </c>
-      <c r="M3" t="n">
-        <v>54155</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>18.04/
 13:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>XIAO MAY BRTG. ON
 18.04/2000, UB 21.04/0600
@@ -636,76 +595,45 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>BERTH-07</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>CAPE LINA/288.97/
 14.000   .  .</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>11.04 12:19
 13.04 19:18
 11.04 12:19</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>C.COAL/I</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>HIRALA/JSW ST</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>/
-9725</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>/
-9868</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>/
-7302</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>/
-26895</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="F5" t="n">
         <v>123500</v>
       </c>
-      <c r="L4" t="n">
-        <v>93875</v>
-      </c>
-      <c r="M4" t="n">
-        <v>29625</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>19.04/
 03:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>NEWCASTLE EXPRESS BRTG. ON
 19.04/0900 (ACTUAL BRTG. TO
@@ -714,284 +642,684 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>BERTH-08</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>HARVEST/179.80/
 12.100   .  .</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>15.04 12:08
 15.04 14:12
 15.04 13:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>MS    /I</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>HINDUS/HP</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>/
-3130</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>/
-3130</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="F6" t="n">
         <v>6000</v>
       </c>
-      <c r="L5" t="n">
-        <v>3130</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2870</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>17.04/
 16:30</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>HSD COMPLETED</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>BERTH-09</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>TUG TAG
 SHIV/26.10 /
 6.800   .  .</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>19.06 12:14
 19.06 12:54</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>/I</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>JOANES</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>BERTH-09</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>FNS KNS ROKS DAE
 JO YEONG/150.00/
 10.000   .  .</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>14.04 08:19
 14.04 10:20</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>/I</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>ISS SH</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>17.04/
 18:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>BERTH-10</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>SWARNA
 PUSHP/184.95   .
 .</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>17.04 00:01
 17.04 02:24</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>LSHF  /I</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>SAMSAR/IOCL</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>/
-264</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>/
-264</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="F9" t="n">
         <v>3000</v>
       </c>
-      <c r="L8" t="n">
-        <v>264</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2736</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>17.04/
 15:30</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BERTH-11</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>.  .</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BERTH-BW</t>
+          <t>BERTH-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CGS CG18 (GSL
-YARD</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>01.04 00:01
-14.04 13:48</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>/I</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>THE CO</t>
-        </is>
-      </c>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BERTH-BW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CGS CG18 (GSL
+YARD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01.04 00:01
+14.04 13:48</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>/I</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>THE CO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>30.04</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BERTH-BW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BARGE ROYAL
+PAMBA/38.00 /
+1.850   .  .</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>01.04 12:00
+16.04 13:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>/I</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SHAHI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SEVEN SEAS MARINER BRTG.
+19.04/0545, UB 19.04/1830
+(ACTUAL BRTG. TO BE
+FINALISED BY MARINE DEPT.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FJ02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CGS CG242/50.00 /
+4.500   .  .</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>01.04 00:01
+16.04 12:35</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>/I</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>THE CO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FJ05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ROYAL SESA/92.00
+/    4.000   .  .</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>01.04 00:01
+09.04 11:12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>/I</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SESA M</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SHIFTING TO WOB ON
+19.04/1000. GOING A/S CHORUS
+AT WOB ON 20.04/0900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FJ06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>YELLOW FIN/35.76
+/    0.000   .  .</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>28.02 07:25
+28.11 17:30</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>/I</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MD-1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MD-2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>:      :
+   :</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>/
+  :</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MD-3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>:      :
+   :</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>/
+  :</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MD-4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>:      :
+   :</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>/
+  :</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MD-5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>:      :
+   :</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>/
+  :</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MD-6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>:      :
+   :</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>/
+  :</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MOLE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>INS T61/46.00 /
+2.500   .  .</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>12.04 12:12
+16.04 11:54</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>/I</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>FLAG O</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>31.05</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>M-LAURA-1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MALLINATH</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>.  .</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ZAHAB JAHAN
+I/189.99/
+12.700   .  .</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11.04 00:27
+11.04 02:00
+11.04 00:27</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>I_FINE/E</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HIRALA/JSW ST</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>56200</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>18.04/
+15:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>APJ
+SHIRIN/189.99/
+13.000   .  .</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16.04 05:17
+16.04 06:30
+16.04 05:17</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>I_FINE/E</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ATLANT/ VEDAN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>56480</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>21.04/
+15:00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mormugao/test.xlsx
+++ b/mormugao/test.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,32 +445,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ARR/BER/NO</t>
+          <t>ETA1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>CARGO/I/E</t>
+          <t>ETB1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>AGENT/SHPR-RECVR/STEVHOOK/</t>
+          <t>ETD</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>QTY I</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ETD</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>AGENT</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SHIPPER/RECEIVER</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>REMARKS</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ETB</t>
         </is>
       </c>
     </row>
@@ -478,33 +507,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VISHAL HIRA/92.37
-/    3.500   .  .</t>
+          <t>VISHAL HIRA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01.04 00:01
-01.04 00:01</t>
+          <t>01-04 00:01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/I</t>
+          <t>01-04 00:01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>V.M. S</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>46113.00069444445</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>46113.00069444445</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -515,37 +555,55 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>OCEAN
-HELIOS/182.93   .
-.</t>
+HELIOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14.04 05:03
-14.04 07:06
-14.04 05:03</t>
+          <t>14-04 05:03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HR COI/E</t>
+          <t>14-04 07:06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>BENLIN/JSW ST</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>37934</v>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>18.04/
 16:00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HR COI</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>37934</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BENLIN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>JSW ST</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" s="2" t="n">
+        <v>46126.21041666667</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>46126.21041666667</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -556,37 +614,45 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>LUCKY
-SUNDAY/229.00   .
-.</t>
+SUNDAY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15.04 07:43
-16.04 19:50
-15.04 07:43</t>
+          <t>15-04 07:43</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C.COAL/I</t>
+          <t>16-04 19:50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>HIRALA</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>72855</v>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>18.04/
 13:00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C.COAL</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>72855</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>HIRALA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>XIAO MAY BRTG. ON
 18.04/2000, UB 21.04/0600
@@ -594,6 +660,12 @@
 FINALISED BY MARINE DEPT.)</t>
         </is>
       </c>
+      <c r="L4" s="2" t="n">
+        <v>46127.32152777778</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>46127.32152777778</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -603,37 +675,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CAPE LINA/288.97/
-14.000   .  .</t>
+          <t>CAPE LINA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11.04 12:19
-13.04 19:18
-11.04 12:19</t>
+          <t>11-04 12:19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C.COAL/I</t>
+          <t>13-04 19:18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
-        <is>
-          <t>HIRALA/JSW ST</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>123500</v>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>19.04/
 03:00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C.COAL</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>123500</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>HIRALA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>JSW ST</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>NEWCASTLE EXPRESS BRTG. ON
 19.04/0900 (ACTUAL BRTG. TO
@@ -641,6 +725,12 @@
 DEPT.)</t>
         </is>
       </c>
+      <c r="L5" s="2" t="n">
+        <v>46123.51319444444</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>46123.51319444444</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -650,40 +740,58 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HARVEST/179.80/
-12.100   .  .</t>
+          <t>HARVEST</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15.04 12:08
-15.04 14:12
-15.04 13:00</t>
+          <t>15-04 12:08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MS    /I</t>
+          <t>15-04 14:12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>HINDUS/HP</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>17.04/
 16:30</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS    </t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>HINDUS</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>HSD COMPLETED</t>
         </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>46127.50555555556</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>46127.50555555556</v>
       </c>
     </row>
     <row r="7">
@@ -695,29 +803,40 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>TUG TAG
-SHIV/26.10 /
-6.800   .  .</t>
+SHIV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19.06 12:14
-19.06 12:54</t>
+          <t>19-06 12:14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>/I</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>JOANES</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>19-06 12:54</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>JOANES</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>46192.50972222222</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>46192.50972222222</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -728,34 +847,45 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>FNS KNS ROKS DAE
-JO YEONG/150.00/
-10.000   .  .</t>
+JO YEONG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14.04 08:19
-14.04 10:20</t>
+          <t>14-04 08:19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>/I</t>
+          <t>14-04 10:20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>ISS SH</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
         <is>
           <t>17.04/
 18:00</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ISS SH</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" s="2" t="n">
+        <v>46126.34652777778</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>46126.34652777778</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -766,36 +896,55 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>SWARNA
-PUSHP/184.95   .
-.</t>
+PUSHP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17.04 00:01
-17.04 02:24</t>
+          <t>17-04 00:01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LSHF  /I</t>
+          <t>17-04 02:24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>SAMSAR/IOCL</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>17.04/
 15:30</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LSHF  </t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SAMSAR</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>IOCL</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>46129.00069444445</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>46129.00069444445</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -805,7 +954,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -814,6 +963,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -829,27 +983,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01.04 00:01
-14.04 13:48</t>
+          <t>01-04 00:01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>/I</t>
+          <t>14-04 13:48</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>THE CO</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" s="2" t="n">
+        <v>46113.00069444445</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>46113.00069444445</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -860,33 +1026,38 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>BARGE ROYAL
-PAMBA/38.00 /
-1.850   .  .</t>
+PAMBA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01.04 12:00
-16.04 13:00</t>
+          <t>01-04 12:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>/I</t>
+          <t>16-04 13:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>SHAHI</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>SEVEN SEAS MARINER BRTG.
 19.04/0545, UB 19.04/1830
@@ -894,6 +1065,12 @@
 FINALISED BY MARINE DEPT.)</t>
         </is>
       </c>
+      <c r="L12" s="2" t="n">
+        <v>46113.5</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>46113.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -903,33 +1080,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CGS CG242/50.00 /
-4.500   .  .</t>
+          <t>CGS CG242</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01.04 00:01
-16.04 12:35</t>
+          <t>01-04 00:01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>/I</t>
+          <t>16-04 12:35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>THE CO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" s="2" t="n">
+        <v>46113.00069444445</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>46113.00069444445</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -939,39 +1127,50 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ROYAL SESA/92.00
-/    4.000   .  .</t>
+          <t>ROYAL SESA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01.04 00:01
-09.04 11:12</t>
+          <t>01-04 00:01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>/I</t>
+          <t>09-04 11:12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>SESA M</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>SHIFTING TO WOB ON
 19.04/1000. GOING A/S CHORUS
 AT WOB ON 20.04/0900</t>
         </is>
       </c>
+      <c r="L14" s="2" t="n">
+        <v>46113.00069444445</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>46113.00069444445</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -981,29 +1180,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YELLOW FIN/35.76
-/    0.000   .  .</t>
+          <t>YELLOW FIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>28.02 07:25
-28.11 17:30</t>
+          <t>28-02 07:25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>/I</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>FISHER</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>28-11 17:30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FISHER</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" s="2" t="n">
+        <v>46081.30902777778</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>46081.30902777778</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1013,7 +1223,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1022,6 +1232,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1031,25 +1246,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>:      :
-   :</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t xml:space="preserve">:      :
+  </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>/
   :</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1059,25 +1283,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>:      :
-   :</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t xml:space="preserve">:      :
+  </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>/
   :</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1087,25 +1320,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>:      :
-   :</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t xml:space="preserve">:      :
+  </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>/
   :</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1115,25 +1357,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>:      :
-   :</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t xml:space="preserve">:      :
+  </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>/
   :</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1143,25 +1394,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>:      :
-   :</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t xml:space="preserve">:      :
+  </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>/
   :</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1171,33 +1431,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INS T61/46.00 /
-2.500   .  .</t>
+          <t>INS T61</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12.04 12:12
-16.04 11:54</t>
+          <t>12-04 12:12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>/I</t>
+          <t>16-04 11:54</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>31.05</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>FLAG O</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>31.05</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" s="2" t="n">
+        <v>46124.50833333333</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>46124.50833333333</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1207,7 +1478,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1216,6 +1487,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1225,7 +1501,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>.  .</t>
+          <t>  </t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1234,6 +1510,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1244,39 +1525,57 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>ZAHAB JAHAN
-I/189.99/
-12.700   .  .</t>
+I</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11.04 00:27
-11.04 02:00
-11.04 00:27</t>
+          <t>11-04 00:27</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>I_FINE/E</t>
+          <t>11-04 02:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>HIRALA/JSW ST</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>56200</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
         <is>
           <t>18.04/
 15:00</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I_FINE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>56200</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>HIRALA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>JSW ST</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" s="2" t="n">
+        <v>46123.01875</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>46123.01875</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1287,39 +1586,57 @@
       <c r="B26" t="inlineStr">
         <is>
           <t>APJ
-SHIRIN/189.99/
-13.000   .  .</t>
+SHIRIN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16.04 05:17
-16.04 06:30
-16.04 05:17</t>
+          <t>16-04 05:17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>I_FINE/E</t>
+          <t>16-04 06:30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>ATLANT/ VEDAN</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>56480</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
         <is>
           <t>21.04/
 15:00</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I_FINE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>56480</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ATLANT</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> VEDAN</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" s="2" t="n">
+        <v>46128.22013888889</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>46128.22013888889</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
